--- a/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_persona_zeroshot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_persona_zeroshot.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15965,7 +15965,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16951,7 +16951,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17631,7 +17631,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17767,7 +17767,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18583,7 +18583,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19433,7 +19433,7 @@
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19858,7 +19858,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20283,7 +20283,7 @@
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20419,7 +20419,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20674,7 +20674,7 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26615,7 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="C2238" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43020,7 +43020,7 @@
       </c>
       <c r="C2505" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43700,7 +43700,7 @@
       </c>
       <c r="C2545" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48443,7 +48443,7 @@
       </c>
       <c r="C2824" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48786,7 +48786,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6554030271031327</v>
+        <v>0.6413234776487152</v>
       </c>
     </row>
     <row r="3">
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.552175932671957</v>
+        <v>0.5214275547647068</v>
       </c>
     </row>
     <row r="4">
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5852479563276929</v>
+        <v>0.5582732075778655</v>
       </c>
     </row>
     <row r="5">
@@ -48816,7 +48816,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7670296889392758</v>
+        <v>0.7698996150387771</v>
       </c>
     </row>
     <row r="6">
@@ -48826,7 +48826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5956457053984664</v>
+        <v>0.5780085864620589</v>
       </c>
     </row>
     <row r="7">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>753.2630612600001</v>
+        <v>1617.849377899998</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2651401130799015</v>
+        <v>0.5694647581485386</v>
       </c>
     </row>
   </sheetData>
